--- a/output/stock_quant_scores/C_balance_df.xlsx
+++ b/output/stock_quant_scores/C_balance_df.xlsx
@@ -1316,7 +1316,9 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>282347000000</v>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -1325,16 +1327,22 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>201972000000</v>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>184948000000</v>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>2088741000000</v>
+      </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
@@ -1348,7 +1356,9 @@
         <v>39319000000</v>
       </c>
       <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>2291413000000</v>
+      </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
@@ -1361,7 +1371,9 @@
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>262033000000</v>
+      </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr"/>
     </row>
